--- a/QLDA_Buoi11_NguyenHoTruongTam_1150080156/Nguyễn Hồ Trường Tam_1150080156_Lab11_QLChiPhi.xlsx
+++ b/QLDA_Buoi11_NguyenHoTruongTam_1150080156/Nguyễn Hồ Trường Tam_1150080156_Lab11_QLChiPhi.xlsx
@@ -5,20 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A.monhoc\BT_QLDA\BT.QLDA\QLDA_Buoi11_NguyenHoTruongTam_1150080156\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BT.QLDA\QLDA_Buoi11_NguyenHoTruongTam_1150080156\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567231CE-E079-46A3-8709-95397A9C90E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C9C95B-9454-4DF4-8086-6B9BE4F9FB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3EDDE9D7-FC49-4A7E-AABC-89EB32EDAE8D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{3EDDE9D7-FC49-4A7E-AABC-89EB32EDAE8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Bài1" sheetId="1" r:id="rId1"/>
     <sheet name="Bài2" sheetId="2" r:id="rId2"/>
     <sheet name="Bài3" sheetId="3" r:id="rId3"/>
     <sheet name="Bài4" sheetId="4" r:id="rId4"/>
-    <sheet name="Bài5" sheetId="5" r:id="rId5"/>
-    <sheet name="Bài6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
+    <sheet name="Bài5" sheetId="5" r:id="rId6"/>
+    <sheet name="Bài6" sheetId="6" r:id="rId7"/>
+    <sheet name="III" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="111">
   <si>
     <t>Discount rate</t>
   </si>
@@ -88,9 +90,6 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Vì NPV của project 2 &gt; project 1 ($3612 &gt; $2316) nên project 2 được chọn</t>
-  </si>
-  <si>
     <t>Assume the project is complete in Year 0</t>
   </si>
   <si>
@@ -142,36 +141,6 @@
     <t>BAC</t>
   </si>
   <si>
-    <t>Thời gian KH</t>
-  </si>
-  <si>
-    <t>CV - Cost Variance</t>
-  </si>
-  <si>
-    <t>SV - Schedule Variance</t>
-  </si>
-  <si>
-    <t>CPI - Cost Performance Index</t>
-  </si>
-  <si>
-    <t>SPI - Schedule Performance Index</t>
-  </si>
-  <si>
-    <t>Vì CV = -5000 nên dự án vượt ngân sách</t>
-  </si>
-  <si>
-    <t>Vì SV= -3000 nên dự án chận tiến độ</t>
-  </si>
-  <si>
-    <t>Vì CPI =0.8 &lt;1 nên dự án kém hiệu quả về chi phí</t>
-  </si>
-  <si>
-    <t>Thời gian dự kiến</t>
-  </si>
-  <si>
-    <t>Dự án cần khoảng 1,15 năm để hoàn thành</t>
-  </si>
-  <si>
     <t>Tổng số việc</t>
   </si>
   <si>
@@ -284,6 +253,129 @@
   </si>
   <si>
     <t>Thời gian hoàn thành dự kiến (tuần)</t>
+  </si>
+  <si>
+    <t>NPV Project 2 &gt; Project 1 ($3612 &gt; $2316) =&gt; Chọn Project 2</t>
+  </si>
+  <si>
+    <t>Câu 1</t>
+  </si>
+  <si>
+    <t>Câu 2</t>
+  </si>
+  <si>
+    <t>CV = EV − AC</t>
+  </si>
+  <si>
+    <t>SV = EV − PV</t>
+  </si>
+  <si>
+    <t>CPI = EV / AC</t>
+  </si>
+  <si>
+    <t>SPI = EV / PV</t>
+  </si>
+  <si>
+    <t>Thời gian kế hoạch (năm)</t>
+  </si>
+  <si>
+    <t>Thời gian dự kiến hoàn thành (năm)</t>
+  </si>
+  <si>
+    <t>Nhận định tiến độ (SV&lt;0 và SPI&lt;1 ⇒ chậm)</t>
+  </si>
+  <si>
+    <t>Câu 3 (đánh giá theo CPI)</t>
+  </si>
+  <si>
+    <t>CPI (=EV/AC)</t>
+  </si>
+  <si>
+    <t>Nhận định chi phí (CPI&lt;1 ⇒ vượt chi phí)</t>
+  </si>
+  <si>
+    <t>Câu 4 (ước lượng thời gian)</t>
+  </si>
+  <si>
+    <t>SPI (=EV/PV)</t>
+  </si>
+  <si>
+    <t>Năm</t>
+  </si>
+  <si>
+    <t>Chi phí</t>
+  </si>
+  <si>
+    <t>Lợi ích</t>
+  </si>
+  <si>
+    <t>Dòng tiền (CF)</t>
+  </si>
+  <si>
+    <t>Tổng lợi ích</t>
+  </si>
+  <si>
+    <t>Tổng chi phí</t>
+  </si>
+  <si>
+    <t>TÍNH NPV (GIÁ TRỊ HIỆN TẠI RÒNG)(thông số/giá trị giả)</t>
+  </si>
+  <si>
+    <t>TÍNH ROI (TỶ SUẤT LỢI NHUẬN)(thông số/giá trị giả)</t>
+  </si>
+  <si>
+    <t>TÌM ĐIỂM HOÀ VỐN (PAYBACK)(thông số/giá trị giả)</t>
+  </si>
+  <si>
+    <t>Dòng tiền</t>
+  </si>
+  <si>
+    <t>Lũy kế</t>
+  </si>
+  <si>
+    <t>Payback</t>
+  </si>
+  <si>
+    <t>EVM – Quản lý hiệu quả dự án (2 tháng)</t>
+  </si>
+  <si>
+    <t>1. Xây dựng Dataset ảnh</t>
+  </si>
+  <si>
+    <t>2. Huấn luyện mô hình CNN</t>
+  </si>
+  <si>
+    <t>3. Thiết kế giao diện Flutter</t>
+  </si>
+  <si>
+    <t>4. Kết nối Backend &amp; kiểm thử</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>CV (EV − AC)</t>
+  </si>
+  <si>
+    <t>SV (EV − PV)</t>
+  </si>
+  <si>
+    <t>CPI (EV/AC)</t>
+  </si>
+  <si>
+    <t>SPI (EV/PV)</t>
+  </si>
+  <si>
+    <t>Ước lượng thời gian hoàn thành</t>
+  </si>
+  <si>
+    <t>Thời gian kế hoạch / SPI</t>
+  </si>
+  <si>
+    <t>8 tuần/ SPI</t>
+  </si>
+  <si>
+    <t>tương đương 2 tháng hơn</t>
   </si>
 </sst>
 </file>
@@ -293,7 +385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +414,42 @@
       <family val="1"/>
       <charset val="163"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -374,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -393,9 +521,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -436,6 +561,38 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,7 +929,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41742ED-99D7-4197-BBFB-13651E925421}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.3984375" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -783,7 +940,7 @@
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -795,7 +952,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -803,7 +960,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -826,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -850,7 +1007,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -874,7 +1031,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -898,7 +1055,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -915,7 +1072,7 @@
         <v>2316.346995672176</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -924,7 +1081,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -933,7 +1090,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -956,7 +1113,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -980,7 +1137,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1004,7 +1161,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -1028,7 +1185,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1045,16 +1202,16 @@
         <v>3612.4581654258582</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+    <row r="16" spans="1:7" ht="18" customHeight="1">
+      <c r="A16" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1067,251 +1224,251 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225D6B91-70FD-462A-8536-11D166820F70}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="26.09765625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.8984375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.796875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15" style="10" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" style="10" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="26.09765625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="13.8984375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="15" style="9" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="14.19921875" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22">
+      <c r="B1" s="21">
         <v>0.08</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="8"/>
+      <c r="B3" s="11">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>2</v>
+      </c>
+      <c r="E3" s="11">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12">
-        <v>0</v>
-      </c>
-      <c r="C3" s="12">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12">
-        <v>2</v>
-      </c>
-      <c r="E3" s="12">
-        <v>3</v>
-      </c>
-      <c r="F3" s="9" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>140</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>40</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>40</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>40</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <f>SUM(B4:E4)</f>
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="12">
+    <row r="5" spans="1:6">
+      <c r="A5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.93</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>0.86</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>0.79</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <f t="shared" ref="F5:F6" si="0">SUM(B5:E5)</f>
         <v>3.58</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="9">
+    <row r="6" spans="1:6">
+      <c r="A6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="8">
         <f>B4*B5</f>
         <v>140</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <f t="shared" ref="C6:E6" si="1">C4*C5</f>
         <v>37.200000000000003</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f t="shared" si="1"/>
         <v>34.4</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f t="shared" si="1"/>
         <v>31.6</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f t="shared" si="0"/>
         <v>243.2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="12">
+      <c r="B8" s="8"/>
+      <c r="C8" s="11">
         <v>200</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>200</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>200</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <f>SUM(B8:E8)</f>
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="12">
+    <row r="9" spans="1:6">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>0.93</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>0.86</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>0.79</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <f t="shared" ref="F9:F10" si="2">SUM(B9:E9)</f>
         <v>3.58</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="9">
+    <row r="10" spans="1:6">
+      <c r="A10" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="8">
         <f>B8*B9</f>
         <v>0</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <f t="shared" ref="C10:E10" si="3">C8*C9</f>
         <v>186</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <f t="shared" si="3"/>
         <v>172</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f t="shared" si="3"/>
         <v>158</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <f t="shared" si="2"/>
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="9">
+    <row r="11" spans="1:6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="8">
         <f>F10-F6</f>
         <v>272.8</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="9">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="8">
         <f>B12</f>
         <v>272.8</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="9">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="8">
         <f>(F10-F6)/F6</f>
         <v>1.1217105263157896</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1321,127 +1478,127 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF194F6-C4D5-489C-BF75-83AA319DADBE}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="15.09765625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="14.8984375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.69921875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="14.09765625" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="15.09765625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="14.8984375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="14.69921875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.09765625" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="11">
         <v>0</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>140000</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>0</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <f>B2</f>
         <v>140000</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <f>C2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+    <row r="3" spans="1:5">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>37200</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>186000</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <f>D2+B3</f>
         <v>177200</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <f>E2+C3</f>
         <v>186000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+    <row r="4" spans="1:5">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>34400</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>172000</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <f t="shared" ref="D4:D5" si="0">D3+B4</f>
         <v>211600</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <f t="shared" ref="E4:E5" si="1">E3+C4</f>
         <v>358000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:5">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>31600</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>158000</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <f t="shared" si="0"/>
         <v>243200</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f t="shared" si="1"/>
         <v>516000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="10">
+    <row r="6" spans="1:5">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="9">
         <f>A2 + (D2-E2) / (C3-B3)</f>
         <v>0.94086021505376349</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1450,118 +1607,324 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A83E49-1AC8-4DB1-AE7B-1FDA0AC14018}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="30.69921875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="17.69921875" style="10" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="41.796875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" style="9" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="20">
+    <row r="1" spans="1:2">
+      <c r="A1" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="19">
         <v>23000</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="20">
+    <row r="2" spans="1:2">
+      <c r="A2" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="19">
         <v>20000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="19">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="20">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>120000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="21">
+    <row r="5" spans="1:2">
+      <c r="A5" s="8"/>
+      <c r="B5" s="25"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="26"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="20">
         <f>B2-B3</f>
         <v>-5000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="21">
+    <row r="8" spans="1:2">
+      <c r="A8" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="20">
         <f>B2-B1</f>
         <v>-3000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="10">
+    <row r="9" spans="1:2">
+      <c r="A9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="9">
         <f>B2/B3</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="10">
+    <row r="10" spans="1:2">
+      <c r="A10" s="24"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="9">
         <f>B2/B1</f>
         <v>0.86956521739130432</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="10">
-        <f>B5/B10</f>
+    <row r="13" spans="1:2" ht="12" customHeight="1">
+      <c r="A13" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="9" t="str">
+        <f>"SV="&amp;TEXT(B7,"0,0")&amp;" ; SPI="&amp;TEXT(B10,"0,000")</f>
+        <v>SV=-5000,0 ; SPI=0,000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="12" customHeight="1"/>
+    <row r="15" spans="1:2">
+      <c r="A15" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="20">
+        <f>B8</f>
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="9" t="str">
+        <f>"CPI="&amp;TEXT(B12,"0,00")</f>
+        <v>CPI=0,87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="9">
+        <f>B2/B1</f>
+        <v>0.86956521739130432</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="9">
+        <f>B21/B20</f>
         <v>1.1500000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BC03AD-AC36-4970-B4F0-BC4F94260BC2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB2C8B5-DDF2-4400-855A-338F0BEF3DF5}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="19.09765625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="15.296875" style="9" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>42</v>
+    <row r="3" spans="1:3">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="11"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="11"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="9">
+        <f>SUM(C2:C4)</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="26.4">
+      <c r="A12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="9">
+        <f>(B2*B6) + (B3*B6) + (B4*B6)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="9">
+        <f>((B7/B8)*B9)*B6</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="9">
+        <f>B12/B11</f>
+        <v>0.78947368421052633</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="9">
+        <f>B12/B13</f>
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>
@@ -1569,151 +1932,300 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB2C8B5-DDF2-4400-855A-338F0BEF3DF5}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956BCC47-36B6-471E-BD40-222FCD8AEEA8}">
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.09765625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="15.296875" style="10" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="22.8984375" style="9" customWidth="1"/>
+    <col min="2" max="7" width="8.796875" style="9"/>
+    <col min="8" max="8" width="18.8984375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="17.19921875" style="9" customWidth="1"/>
+    <col min="10" max="10" width="14.59765625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="14.69921875" style="9" customWidth="1"/>
+    <col min="12" max="12" width="14.59765625" style="9" customWidth="1"/>
+    <col min="13" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:12" ht="27" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="L1" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="11">
+        <v>4</v>
+      </c>
+      <c r="C2" s="11">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>5</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="13">
+        <v>2</v>
+      </c>
+      <c r="K2" s="13">
+        <v>2</v>
+      </c>
+      <c r="L2" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="11">
+        <v>6</v>
+      </c>
+      <c r="C3" s="11">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11">
+        <v>7</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="13">
+        <v>3</v>
+      </c>
+      <c r="K3" s="13">
+        <v>2</v>
+      </c>
+      <c r="L3" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="C4" s="11">
+        <v>5</v>
+      </c>
+      <c r="D4" s="11">
+        <v>7</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="K4" s="13">
+        <v>3</v>
+      </c>
+      <c r="L4" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="11">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="H5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="13">
+        <v>3</v>
+      </c>
+      <c r="K5" s="13">
+        <v>2</v>
+      </c>
+      <c r="L5" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="11">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="H6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="13">
+        <v>2</v>
+      </c>
+      <c r="K6" s="13">
+        <v>4</v>
+      </c>
+      <c r="L6" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.4" thickBot="1">
+      <c r="A7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="11">
+        <f>SUM(B2:B6)</f>
+        <v>31.5</v>
+      </c>
+      <c r="C7" s="11">
+        <f>SUM(C2:C6)</f>
+        <v>17</v>
+      </c>
+      <c r="D7" s="11">
+        <f>SUM(D2:D6)</f>
+        <v>19</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="13">
+        <f>SUM(L2:L6)</f>
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="B11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="15">
+        <f>C2/D2</f>
         <v>1</v>
       </c>
-      <c r="B2" s="18">
+      <c r="C12" s="9">
+        <f>C2/B2</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="9">
+        <f>C3/D3</f>
         <v>1</v>
       </c>
-      <c r="C2" s="10">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="12"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="12"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="10">
-        <f>SUM(C2:C4)</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="10">
-        <f>(B2*B6) + (B3*B6) + (B4*B6)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="10">
-        <f>((B7/B8)*B9)*B6</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="10">
-        <f>B12/B11</f>
-        <v>0.78947368421052633</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="10">
-        <f>B12/B13</f>
-        <v>0.625</v>
+      <c r="C13" s="9">
+        <f>C3/B3</f>
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="9">
+        <f>C4/D4</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="C14" s="9">
+        <f>C4/B4</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="9">
+        <f>C7/D7</f>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="C15" s="9">
+        <f>C7/B7</f>
+        <v>0.53968253968253965</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="27.6">
+      <c r="A17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="9">
+        <f>B9/C15</f>
+        <v>22.235294117647062</v>
       </c>
     </row>
   </sheetData>
@@ -1721,300 +2233,416 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956BCC47-36B6-471E-BD40-222FCD8AEEA8}">
-  <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4AA74F-F652-4F11-B0CB-2BCA77B6D46E}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="10" customWidth="1"/>
-    <col min="2" max="7" width="8.796875" style="10"/>
-    <col min="8" max="8" width="18.8984375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="17.19921875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="14.59765625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="14.69921875" style="10" customWidth="1"/>
-    <col min="12" max="12" width="14.59765625" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="8.796875" style="10"/>
+    <col min="1" max="1" width="8.796875" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="12">
+    <row r="1" spans="1:4">
+      <c r="A1" s="35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.6">
+      <c r="A2" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="30">
+        <v>0</v>
+      </c>
+      <c r="B3" s="32">
+        <v>7000</v>
+      </c>
+      <c r="C3" s="30">
+        <v>0</v>
+      </c>
+      <c r="D3" s="32">
+        <v>-7000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="30">
+        <v>1</v>
+      </c>
+      <c r="B4" s="32">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="32">
+        <v>3000</v>
+      </c>
+      <c r="D4" s="32">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="30">
+        <v>2</v>
+      </c>
+      <c r="B5" s="32">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="32">
+        <v>4000</v>
+      </c>
+      <c r="D5" s="32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="30">
+        <v>3</v>
+      </c>
+      <c r="B6" s="32">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="32">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="32">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="30">
         <v>4</v>
       </c>
-      <c r="C2" s="12">
-        <v>5</v>
-      </c>
-      <c r="D2" s="12">
-        <v>5</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="14">
+      <c r="B7" s="32">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="32">
+        <v>6000</v>
+      </c>
+      <c r="D7" s="32">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="31">
+        <f>NPV(10%, D4:D7) + D3</f>
+        <v>3717.847141588687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.6">
+      <c r="A10" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="67.8">
+      <c r="A11" s="32">
+        <v>18000</v>
+      </c>
+      <c r="B11" s="32">
+        <v>11000</v>
+      </c>
+      <c r="C11" s="33">
+        <f>(A11-B11)/B11</f>
+        <v>0.63636363636363635</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27.6">
+      <c r="A13" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="30">
+        <v>0</v>
+      </c>
+      <c r="B14" s="32">
+        <v>-7000</v>
+      </c>
+      <c r="C14" s="32">
+        <f>B14</f>
+        <v>-7000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="30">
+        <v>1</v>
+      </c>
+      <c r="B15" s="32">
+        <v>2000</v>
+      </c>
+      <c r="C15" s="32">
+        <f>C14+B15</f>
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="30">
         <v>2</v>
       </c>
-      <c r="K2" s="14">
+      <c r="B16" s="32">
+        <v>3000</v>
+      </c>
+      <c r="C16" s="32">
+        <f>C15+B16</f>
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="30">
+        <v>3</v>
+      </c>
+      <c r="B17" s="32">
+        <v>4000</v>
+      </c>
+      <c r="C17" s="32">
+        <f>C16+B17</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18">
+        <f>2 + (ABS(C16)/(B17))</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="27.6">
+      <c r="A20" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="55.2">
+      <c r="A21" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="28">
+        <v>3</v>
+      </c>
+      <c r="C21" s="28">
+        <v>3</v>
+      </c>
+      <c r="D21" s="28">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <f>C21-D21</f>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f>C21-B21</f>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f>IF(D21&gt;0,C21/D21,NA())</f>
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <f>IF(B21&gt;0,C21/B21,NA())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="41.4">
+      <c r="A22" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="28">
+        <v>4</v>
+      </c>
+      <c r="C22" s="28">
+        <v>3</v>
+      </c>
+      <c r="D22" s="28">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <f>C22-D22</f>
+        <v>-1</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:F24" si="0">C22-B22</f>
+        <v>-1</v>
+      </c>
+      <c r="G22">
+        <f t="shared" ref="G22:G24" si="1">IF(D22&gt;0,C22/D22,NA())</f>
+        <v>0.75</v>
+      </c>
+      <c r="H22">
+        <f t="shared" ref="H22:H24" si="2">IF(B22&gt;0,C22/B22,NA())</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="55.2">
+      <c r="A23" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="28">
+        <v>3</v>
+      </c>
+      <c r="C23" s="28">
         <v>2</v>
       </c>
-      <c r="L2" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="12">
-        <v>6</v>
-      </c>
-      <c r="C3" s="12">
-        <v>7</v>
-      </c>
-      <c r="D3" s="12">
-        <v>7</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="J3" s="14">
-        <v>3</v>
-      </c>
-      <c r="K3" s="14">
+      <c r="D23" s="28">
         <v>2</v>
       </c>
-      <c r="L3" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="12">
-        <v>7.5</v>
-      </c>
-      <c r="C4" s="12">
-        <v>5</v>
-      </c>
-      <c r="D4" s="12">
-        <v>7</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="K4" s="14">
-        <v>3</v>
-      </c>
-      <c r="L4" s="14">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="12">
-        <v>6</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="H5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="14">
-        <v>3</v>
-      </c>
-      <c r="K5" s="14">
+      <c r="E23">
+        <f t="shared" ref="E23:E24" si="3">C23-D23</f>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="55.2">
+      <c r="A24" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="28">
         <v>2</v>
       </c>
-      <c r="L5" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="12">
-        <v>8</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="H6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="14">
+      <c r="C24" s="28">
+        <v>1</v>
+      </c>
+      <c r="D24" s="28">
         <v>2</v>
       </c>
-      <c r="K6" s="14">
-        <v>4</v>
-      </c>
-      <c r="L6" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="12">
-        <f>SUM(B2:B6)</f>
-        <v>31.5</v>
-      </c>
-      <c r="C7" s="12">
-        <f>SUM(C2:C6)</f>
-        <v>17</v>
-      </c>
-      <c r="D7" s="12">
-        <f>SUM(D2:D6)</f>
-        <v>19</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="14">
-        <f>SUM(L2:L6)</f>
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="E24">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="29">
+        <f>SUM(B21:B24)</f>
         <v>12</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="16">
-        <f>C2/D2</f>
-        <v>1</v>
-      </c>
-      <c r="C12" s="10">
-        <f>C2/B2</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="10">
-        <f>C3/D3</f>
-        <v>1</v>
-      </c>
-      <c r="C13" s="10">
-        <f>C3/B3</f>
-        <v>1.1666666666666667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="10">
-        <f>C4/D4</f>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="C14" s="10">
-        <f>C4/B4</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="10">
-        <f>C7/D7</f>
-        <v>0.89473684210526316</v>
-      </c>
-      <c r="C15" s="10">
-        <f>C7/B7</f>
-        <v>0.53968253968253965</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="10">
-        <f>B9/C15</f>
-        <v>22.235294117647062</v>
+      <c r="C25" s="29">
+        <f>SUM(C21:C24)</f>
+        <v>9</v>
+      </c>
+      <c r="D25" s="29">
+        <f>SUM(D21:D24)</f>
+        <v>11</v>
+      </c>
+      <c r="E25">
+        <f>C25-D25</f>
+        <v>-2</v>
+      </c>
+      <c r="F25">
+        <f>C25-B25</f>
+        <v>-3</v>
+      </c>
+      <c r="G25">
+        <f>C25/D25</f>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="H25">
+        <f>C25/B25</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="69">
+      <c r="A26" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26">
+        <f>8/H25</f>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="G26" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
